--- a/tools/importer/reports/import-product-page.report.xlsx
+++ b/tools/importer/reports/import-product-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="112">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,51 @@
     <t>url</t>
   </si>
   <si>
+    <t>us/en.report.json</t>
+  </si>
+  <si>
+    <t>["embed","columns","columns","columns","columns","columns","columns","columns","cards","cards","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>us/en</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>homepage</t>
+  </si>
+  <si>
+    <t>2026-04-28T11:06:38.643Z</t>
+  </si>
+  <si>
+    <t>Stryker - Medical Devices and Equipment Manufacturing Company | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/index.html</t>
+  </si>
+  <si>
+    <t>us/en/training-and-education.report.json</t>
+  </si>
+  <si>
+    <t>["embed","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>us/en/training-and-education</t>
+  </si>
+  <si>
+    <t>hub-page</t>
+  </si>
+  <si>
+    <t>2026-04-28T09:58:27.456Z</t>
+  </si>
+  <si>
+    <t>Training and education | Stryker</t>
+  </si>
+  <si>
+    <t>https://www.stryker.com/us/en/training-and-education.html</t>
+  </si>
+  <si>
     <t>us/en/portfolios/medical-surgical-equipment/integration-and-connectivity/or-integration/rise.report.json</t>
   </si>
   <si>
@@ -46,13 +91,10 @@
     <t>us/en/portfolios/medical-surgical-equipment/integration-and-connectivity/or-integration/rise</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-04-28T09:29:20.137Z</t>
+    <t>2026-04-28T11:53:27.329Z</t>
   </si>
   <si>
     <t>RISE | Stryker</t>
@@ -73,7 +115,7 @@
     <t>training-article</t>
   </si>
   <si>
-    <t>2026-04-24T08:09:47.636Z</t>
+    <t>2026-04-28T11:51:20.661Z</t>
   </si>
   <si>
     <t>Cardiovascular health | Stryker</t>
@@ -91,7 +133,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/caregiver-safety</t>
   </si>
   <si>
-    <t>2026-04-24T08:09:54.150Z</t>
+    <t>2026-04-28T11:51:27.992Z</t>
   </si>
   <si>
     <t>Caregiver safety | Stryker</t>
@@ -109,7 +151,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/cerebrovascular-health</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:00.666Z</t>
+    <t>2026-04-28T11:51:32.870Z</t>
   </si>
   <si>
     <t>Cerebrovascular health | Stryker</t>
@@ -124,7 +166,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/complex-surgical-access-and-decompression</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:06.477Z</t>
+    <t>2026-04-28T11:51:37.409Z</t>
   </si>
   <si>
     <t>Complex surgical access and decompression | Stryker</t>
@@ -139,7 +181,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/cranial-procedures-and-repair</t>
   </si>
   <si>
-    <t>2026-04-24T08:06:45.172Z</t>
+    <t>2026-04-28T11:52:37.368Z</t>
   </si>
   <si>
     <t>Cranial procedures and repair | Stryker</t>
@@ -157,7 +199,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/fall-prevention</t>
   </si>
   <si>
-    <t>2026-04-24T08:06:40.590Z</t>
+    <t>2026-04-28T11:52:31.980Z</t>
   </si>
   <si>
     <t>Fall prevention | Stryker</t>
@@ -175,7 +217,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/healthcare-teamwork-and-communication</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:12.773Z</t>
+    <t>2026-04-28T11:51:41.716Z</t>
   </si>
   <si>
     <t>Healthcare teamwork and communication | Stryker</t>
@@ -193,7 +235,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/hospital-acquired-infections</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:18.427Z</t>
+    <t>2026-04-28T11:51:49.602Z</t>
   </si>
   <si>
     <t>Hospital-acquired infections | Stryker</t>
@@ -211,7 +253,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/mobility</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:22.735Z</t>
+    <t>2026-04-28T11:51:56.544Z</t>
   </si>
   <si>
     <t>Mobility | Stryker</t>
@@ -229,7 +271,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/pressure-injuries</t>
   </si>
   <si>
-    <t>2026-04-24T07:52:34.920Z</t>
+    <t>2026-04-28T11:51:16.410Z</t>
   </si>
   <si>
     <t>Pressure injuries | Stryker</t>
@@ -247,7 +289,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/surgical-access-and-visualization</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:27.863Z</t>
+    <t>2026-04-28T11:52:02.706Z</t>
   </si>
   <si>
     <t>Surgical access and visualization | Stryker</t>
@@ -265,7 +307,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/upcoming-events</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:39.836Z</t>
+    <t>2026-04-28T11:52:13.855Z</t>
   </si>
   <si>
     <t>FocusRN upcoming events | Stryker</t>
@@ -283,7 +325,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/waste-management-practices</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:47.019Z</t>
+    <t>2026-04-28T11:52:21.602Z</t>
   </si>
   <si>
     <t>Waste management practices | Stryker</t>
@@ -298,7 +340,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/womens-health</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:53.126Z</t>
+    <t>2026-04-28T11:52:26.978Z</t>
   </si>
   <si>
     <t>Women's health | Stryker</t>
@@ -693,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -794,328 +836,380 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-product-page.report.xlsx
+++ b/tools/importer/reports/import-product-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-28T11:06:38.643Z</t>
+    <t>2026-04-28T11:53:35.840Z</t>
   </si>
   <si>
     <t>Stryker - Medical Devices and Equipment Manufacturing Company | Stryker</t>
@@ -73,7 +73,7 @@
     <t>hub-page</t>
   </si>
   <si>
-    <t>2026-04-28T09:58:27.456Z</t>
+    <t>2026-04-28T11:53:31.377Z</t>
   </si>
   <si>
     <t>Training and education | Stryker</t>
@@ -94,7 +94,7 @@
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-04-28T11:53:27.329Z</t>
+    <t>2026-04-28T12:07:39.104Z</t>
   </si>
   <si>
     <t>RISE | Stryker</t>
@@ -115,7 +115,7 @@
     <t>training-article</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:20.661Z</t>
+    <t>2026-04-28T12:06:03.051Z</t>
   </si>
   <si>
     <t>Cardiovascular health | Stryker</t>
@@ -133,7 +133,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/caregiver-safety</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:27.992Z</t>
+    <t>2026-04-28T12:06:09.357Z</t>
   </si>
   <si>
     <t>Caregiver safety | Stryker</t>
@@ -151,7 +151,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/cerebrovascular-health</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:32.870Z</t>
+    <t>2026-04-28T12:06:15.175Z</t>
   </si>
   <si>
     <t>Cerebrovascular health | Stryker</t>
@@ -166,7 +166,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/complex-surgical-access-and-decompression</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:37.409Z</t>
+    <t>2026-04-28T12:06:21.354Z</t>
   </si>
   <si>
     <t>Complex surgical access and decompression | Stryker</t>
@@ -181,7 +181,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/cranial-procedures-and-repair</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:37.368Z</t>
+    <t>2026-04-28T12:07:17.709Z</t>
   </si>
   <si>
     <t>Cranial procedures and repair | Stryker</t>
@@ -199,7 +199,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/fall-prevention</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:31.980Z</t>
+    <t>2026-04-28T12:07:13.282Z</t>
   </si>
   <si>
     <t>Fall prevention | Stryker</t>
@@ -217,7 +217,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/healthcare-teamwork-and-communication</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:41.716Z</t>
+    <t>2026-04-28T12:06:25.625Z</t>
   </si>
   <si>
     <t>Healthcare teamwork and communication | Stryker</t>
@@ -235,7 +235,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/hospital-acquired-infections</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:49.602Z</t>
+    <t>2026-04-28T12:06:31.050Z</t>
   </si>
   <si>
     <t>Hospital-acquired infections | Stryker</t>
@@ -253,7 +253,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/mobility</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:56.544Z</t>
+    <t>2026-04-28T12:06:35.678Z</t>
   </si>
   <si>
     <t>Mobility | Stryker</t>
@@ -271,7 +271,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/pressure-injuries</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:16.410Z</t>
+    <t>2026-04-28T12:05:59.115Z</t>
   </si>
   <si>
     <t>Pressure injuries | Stryker</t>
@@ -289,7 +289,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/surgical-access-and-visualization</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:02.706Z</t>
+    <t>2026-04-28T12:06:40.023Z</t>
   </si>
   <si>
     <t>Surgical access and visualization | Stryker</t>
@@ -307,7 +307,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/upcoming-events</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:13.855Z</t>
+    <t>2026-04-28T12:06:59.663Z</t>
   </si>
   <si>
     <t>FocusRN upcoming events | Stryker</t>
@@ -325,7 +325,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/waste-management-practices</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:21.602Z</t>
+    <t>2026-04-28T12:07:04.828Z</t>
   </si>
   <si>
     <t>Waste management practices | Stryker</t>
@@ -340,7 +340,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/womens-health</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:26.978Z</t>
+    <t>2026-04-28T12:07:09.336Z</t>
   </si>
   <si>
     <t>Women's health | Stryker</t>
